--- a/Words(音读音 & 训练音).xlsx
+++ b/Words(音读音 & 训练音).xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094D56C1-6D0C-4A9B-AD69-232015AD291E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27816C1-72BC-4B24-8545-6034970324DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3996" yWindow="996" windowWidth="16200" windowHeight="11076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Object(もの)" sheetId="6" r:id="rId1"/>
     <sheet name="Common" sheetId="1" state="hidden" r:id="rId2"/>
     <sheet name="Cloth（いふく）" sheetId="11" r:id="rId3"/>
     <sheet name="食べ物（たべもの）" sheetId="8" r:id="rId4"/>
-    <sheet name="LifeStyle（せいかつ）" sheetId="5" r:id="rId5"/>
+    <sheet name="LifeStyle（せいかつようしき）" sheetId="5" r:id="rId5"/>
     <sheet name="愛好（あいこう）" sheetId="12" r:id="rId6"/>
     <sheet name="芸術（げいじゅつ）" sheetId="14" r:id="rId7"/>
     <sheet name="url" sheetId="2" r:id="rId8"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="936">
   <si>
     <t>木</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4183,6 +4183,14 @@
   </si>
   <si>
     <t>おうせい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深みにはまる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふかみにはまる</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4977,10 +4985,10 @@
         <v>623</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>656</v>
+        <v>753</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>657</v>
+        <v>754</v>
       </c>
       <c r="I7" s="34" t="s">
         <v>703</v>
@@ -4998,10 +5006,10 @@
         <v>627</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>753</v>
+        <v>664</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>754</v>
+        <v>665</v>
       </c>
       <c r="I8" s="34" t="s">
         <v>700</v>
@@ -5021,10 +5029,10 @@
         <v>707</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I9" s="34" t="s">
         <v>690</v>
@@ -5044,10 +5052,10 @@
         <v>631</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="I10" s="34" t="s">
         <v>812</v>
@@ -5067,10 +5075,10 @@
         <v>649</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="I11" s="34" t="s">
         <v>712</v>
@@ -5090,10 +5098,10 @@
         <v>651</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="I12" s="34" t="s">
         <v>715</v>
@@ -5113,10 +5121,10 @@
         <v>707</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>673</v>
+        <v>729</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>672</v>
+        <v>730</v>
       </c>
       <c r="I13" s="34" t="s">
         <v>755</v>
@@ -5136,10 +5144,10 @@
         <v>708</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="I14" s="34" t="s">
         <v>747</v>
@@ -5156,10 +5164,10 @@
         <v>699</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
       <c r="I15" s="34" t="s">
         <v>756</v>
@@ -5176,10 +5184,13 @@
         <v>734</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>752</v>
+        <v>765</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>766</v>
       </c>
       <c r="I16" s="34" t="s">
         <v>758</v>
@@ -5195,14 +5206,14 @@
       <c r="B17" s="34" t="s">
         <v>746</v>
       </c>
-      <c r="E17" s="34" t="s">
-        <v>764</v>
+      <c r="E17" s="4" t="s">
+        <v>809</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>765</v>
+        <v>810</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>766</v>
+        <v>811</v>
       </c>
       <c r="I17" s="34" t="s">
         <v>889</v>
@@ -5218,14 +5229,11 @@
       <c r="B18" s="34" t="s">
         <v>750</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>809</v>
+      <c r="E18" s="34" t="s">
+        <v>902</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>810</v>
-      </c>
-      <c r="G18" s="34" t="s">
-        <v>811</v>
+        <v>903</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -5236,10 +5244,10 @@
         <v>772</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -5250,10 +5258,10 @@
         <v>774</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>912</v>
+        <v>801</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>913</v>
+        <v>802</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5262,12 +5270,6 @@
       </c>
       <c r="B21" s="34" t="s">
         <v>776</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>801</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7836,6 +7838,9 @@
       <c r="C28" t="s">
         <v>533</v>
       </c>
+      <c r="E28" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="18">
       <c r="A29" s="34" t="s">
@@ -8166,11 +8171,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47639CE2-68F7-4673-A298-E034A868B499}">
-  <dimension ref="A2:L19"/>
+  <dimension ref="A2:L20"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="18.21875" customWidth="1"/>
     <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8439,29 +8445,48 @@
         <v>856</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18">
+    <row r="17" spans="1:7" ht="18">
       <c r="A17" s="34" t="s">
         <v>617</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.6">
-      <c r="A18" s="5" t="s">
+      <c r="F17" s="34" t="s">
+        <v>934</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18">
+      <c r="A18" s="34" t="s">
         <v>680</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="34" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.6">
-      <c r="A19" s="5" t="s">
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="1:7" ht="18">
+      <c r="A19" s="34" t="s">
         <v>682</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="34" t="s">
         <v>683</v>
       </c>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+    </row>
+    <row r="20" spans="1:7" ht="18">
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
